--- a/project/outputs_xlsx_solution/test33.4-wide.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide.xlsx
@@ -831,24 +831,6 @@
       <c r="CI1">
         <v>84</v>
       </c>
-      <c r="CJ1">
-        <v>85</v>
-      </c>
-      <c r="CK1">
-        <v>86</v>
-      </c>
-      <c r="CL1">
-        <v>87</v>
-      </c>
-      <c r="CM1">
-        <v>88</v>
-      </c>
-      <c r="CN1">
-        <v>89</v>
-      </c>
-      <c r="CO1">
-        <v>90</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1183,7 +1165,7 @@
         <v>15</v>
       </c>
       <c r="S13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T13" t="s">
         <v>14</v>
@@ -1195,9 +1177,6 @@
         <v>14</v>
       </c>
       <c r="W13" t="s">
-        <v>14</v>
-      </c>
-      <c r="X13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1232,7 +1211,7 @@
       <c r="O14" t="s">
         <v>21</v>
       </c>
-      <c r="X14" t="s">
+      <c r="W14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1273,7 +1252,7 @@
       <c r="R15" t="s">
         <v>21</v>
       </c>
-      <c r="X15" t="s">
+      <c r="W15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1302,7 +1281,7 @@
       <c r="N16" t="s">
         <v>21</v>
       </c>
-      <c r="X16" t="s">
+      <c r="W16" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1334,7 +1313,7 @@
       <c r="O17" t="s">
         <v>21</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="X17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1363,7 +1342,7 @@
       <c r="N18" t="s">
         <v>21</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="X18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1392,7 +1371,7 @@
       <c r="O19" t="s">
         <v>21</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="X19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1419,7 +1398,7 @@
         <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P20" t="s">
         <v>14</v>
@@ -1431,12 +1410,9 @@
         <v>14</v>
       </c>
       <c r="S20" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y20" t="s">
+        <v>21</v>
+      </c>
+      <c r="X20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1459,6 +1435,9 @@
       <c r="O21" t="s">
         <v>33</v>
       </c>
+      <c r="S21" t="s">
+        <v>14</v>
+      </c>
       <c r="T21" t="s">
         <v>14</v>
       </c>
@@ -1466,12 +1445,9 @@
         <v>14</v>
       </c>
       <c r="V21" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1494,13 +1470,13 @@
       <c r="O22" t="s">
         <v>33</v>
       </c>
+      <c r="V22" t="s">
+        <v>14</v>
+      </c>
       <c r="W22" t="s">
-        <v>14</v>
-      </c>
-      <c r="X22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1521,15 +1497,12 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P23" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y23" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1550,15 +1523,12 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Q24" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1572,22 +1542,19 @@
       <c r="C25" t="s">
         <v>27</v>
       </c>
+      <c r="Q25" t="s">
+        <v>5</v>
+      </c>
       <c r="R25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T25" t="s">
-        <v>33</v>
-      </c>
-      <c r="U25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1601,20 +1568,26 @@
       <c r="C26" t="s">
         <v>28</v>
       </c>
+      <c r="Q26" t="s">
+        <v>5</v>
+      </c>
       <c r="R26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S26" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="T26" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="U26" t="s">
+        <v>15</v>
       </c>
       <c r="V26" t="s">
         <v>15</v>
       </c>
       <c r="W26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1626,9 +1599,6 @@
         <v>14</v>
       </c>
       <c r="AA26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1642,15 +1612,18 @@
       <c r="C27" t="s">
         <v>29</v>
       </c>
+      <c r="Q27" t="s">
+        <v>5</v>
+      </c>
       <c r="R27" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T27" t="s">
         <v>33</v>
       </c>
+      <c r="AA27" t="s">
+        <v>14</v>
+      </c>
       <c r="AB27" t="s">
         <v>14</v>
       </c>
@@ -1658,9 +1631,6 @@
         <v>14</v>
       </c>
       <c r="AD27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1674,19 +1644,19 @@
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="Q28" t="s">
+        <v>5</v>
+      </c>
       <c r="R28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S28" t="s">
-        <v>9</v>
-      </c>
-      <c r="T28" t="s">
         <v>33</v>
       </c>
+      <c r="AD28" t="s">
+        <v>14</v>
+      </c>
       <c r="AE28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1700,11 +1670,14 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="R29" t="s">
+        <v>5</v>
+      </c>
       <c r="S29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T29" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="U29" t="s">
         <v>34</v>
@@ -1713,18 +1686,12 @@
         <v>34</v>
       </c>
       <c r="W29" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="X29" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1738,22 +1705,22 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
+      <c r="R30" t="s">
+        <v>5</v>
+      </c>
       <c r="S30" t="s">
-        <v>5</v>
-      </c>
-      <c r="T30" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W30" t="s">
+        <v>33</v>
       </c>
       <c r="X30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF30" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1767,19 +1734,19 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="S31" t="s">
+        <v>5</v>
+      </c>
       <c r="T31" t="s">
-        <v>5</v>
-      </c>
-      <c r="U31" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W31" t="s">
+        <v>14</v>
       </c>
       <c r="X31" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1793,14 +1760,17 @@
       <c r="C32" t="s">
         <v>28</v>
       </c>
+      <c r="S32" t="s">
+        <v>5</v>
+      </c>
       <c r="T32" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W32" t="s">
+        <v>33</v>
       </c>
       <c r="X32" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Y32" t="s">
         <v>15</v>
@@ -1809,7 +1779,7 @@
         <v>15</v>
       </c>
       <c r="AA32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB32" t="s">
         <v>14</v>
@@ -1821,12 +1791,9 @@
         <v>14</v>
       </c>
       <c r="AE32" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG32" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1840,15 +1807,18 @@
       <c r="C33" t="s">
         <v>29</v>
       </c>
+      <c r="S33" t="s">
+        <v>5</v>
+      </c>
       <c r="T33" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y33" t="s">
+        <v>9</v>
+      </c>
+      <c r="X33" t="s">
         <v>33</v>
       </c>
+      <c r="AE33" t="s">
+        <v>14</v>
+      </c>
       <c r="AF33" t="s">
         <v>14</v>
       </c>
@@ -1856,9 +1826,6 @@
         <v>14</v>
       </c>
       <c r="AH33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI33" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1872,19 +1839,19 @@
       <c r="C34" t="s">
         <v>30</v>
       </c>
+      <c r="S34" t="s">
+        <v>5</v>
+      </c>
       <c r="T34" t="s">
-        <v>5</v>
-      </c>
-      <c r="U34" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y34" t="s">
+        <v>9</v>
+      </c>
+      <c r="X34" t="s">
         <v>33</v>
       </c>
+      <c r="AH34" t="s">
+        <v>14</v>
+      </c>
       <c r="AI34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1898,22 +1865,19 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="T35" t="s">
+        <v>5</v>
+      </c>
       <c r="U35" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="X35" t="s">
+        <v>14</v>
       </c>
       <c r="Y35" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ35" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI35" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1927,22 +1891,22 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
+      <c r="T36" t="s">
+        <v>5</v>
+      </c>
       <c r="U36" t="s">
-        <v>5</v>
-      </c>
-      <c r="V36" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="X36" t="s">
+        <v>33</v>
       </c>
       <c r="Y36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ36" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI36" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1956,25 +1920,25 @@
       <c r="C37" t="s">
         <v>35</v>
       </c>
+      <c r="Z37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>9</v>
+      </c>
       <c r="AB37" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AC37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD37" t="s">
         <v>14</v>
       </c>
       <c r="AE37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ37" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI37" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1988,17 +1952,26 @@
       <c r="C38" t="s">
         <v>36</v>
       </c>
+      <c r="Z38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>9</v>
+      </c>
       <c r="AB38" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AC38" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AD38" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="AE38" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>14</v>
       </c>
       <c r="AG38" t="s">
         <v>14</v>
@@ -2007,12 +1980,9 @@
         <v>14</v>
       </c>
       <c r="AI38" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AJ38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK38" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2026,19 +1996,19 @@
       <c r="C39" t="s">
         <v>37</v>
       </c>
-      <c r="AB39" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC39" t="s">
-        <v>9</v>
+      <c r="Z39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>14</v>
       </c>
       <c r="AE39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK39" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2052,16 +2022,16 @@
       <c r="C40" t="s">
         <v>38</v>
       </c>
-      <c r="AB40" t="s">
-        <v>5</v>
+      <c r="Z40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>14</v>
       </c>
       <c r="AE40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK40" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2075,20 +2045,23 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AC41" t="s">
-        <v>5</v>
+      <c r="AA41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>9</v>
       </c>
       <c r="AD41" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH41" t="s">
         <v>14</v>
@@ -2097,9 +2070,6 @@
         <v>14</v>
       </c>
       <c r="AJ41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK41" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2113,21 +2083,27 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AC42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>9</v>
+      <c r="AA42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>16</v>
       </c>
       <c r="AG42" t="s">
         <v>16</v>
       </c>
       <c r="AH42" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI42" t="s">
         <v>33</v>
       </c>
+      <c r="AJ42" t="s">
+        <v>14</v>
+      </c>
       <c r="AK42" t="s">
         <v>14</v>
       </c>
@@ -2135,9 +2111,6 @@
         <v>14</v>
       </c>
       <c r="AM42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN42" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2151,20 +2124,23 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AC43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI43" t="s">
+      <c r="AA43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH43" t="s">
         <v>33</v>
       </c>
+      <c r="AM43" t="s">
+        <v>15</v>
+      </c>
       <c r="AN43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP43" t="s">
         <v>14</v>
@@ -2173,6 +2149,12 @@
         <v>14</v>
       </c>
       <c r="AR43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT43" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2186,11 +2168,14 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AC44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>9</v>
+      <c r="AA44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>14</v>
       </c>
       <c r="AI44" t="s">
         <v>14</v>
@@ -2202,12 +2187,9 @@
         <v>14</v>
       </c>
       <c r="AL44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR44" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT44" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2221,11 +2203,14 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AD45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>9</v>
+      <c r="AB45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>14</v>
       </c>
       <c r="AI45" t="s">
         <v>14</v>
@@ -2243,12 +2228,9 @@
         <v>14</v>
       </c>
       <c r="AN45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO45" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR45" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT45" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2262,19 +2244,19 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AD46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>9</v>
+      <c r="AB46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>14</v>
       </c>
       <c r="AJ46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK46" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR46" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT46" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2288,22 +2270,22 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AD47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>9</v>
+      <c r="AB47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>15</v>
       </c>
       <c r="AJ47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS47" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU47" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2317,22 +2299,19 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
+      <c r="AB48" t="s">
+        <v>5</v>
+      </c>
       <c r="AD48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>14</v>
       </c>
       <c r="AJ48" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL48" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS48" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2346,25 +2325,22 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
+      <c r="AC49" t="s">
+        <v>5</v>
+      </c>
       <c r="AE49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>33</v>
       </c>
       <c r="AJ49" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AK49" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM49" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS49" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU49" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2378,46 +2354,34 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
+      <c r="AC50" t="s">
+        <v>5</v>
+      </c>
       <c r="AE50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>16</v>
       </c>
       <c r="AK50" t="s">
         <v>16</v>
       </c>
       <c r="AL50" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM50" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AN50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP50" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ50" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR50" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS50" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT50" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AU50" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV50" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2431,25 +2395,28 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AE51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM51" t="s">
+      <c r="AC51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL51" t="s">
         <v>33</v>
       </c>
+      <c r="AP51" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>21</v>
+      </c>
       <c r="AV51" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW51" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX51" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY51" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2463,19 +2430,22 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AE52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM52" t="s">
+      <c r="AD52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL52" t="s">
         <v>33</v>
       </c>
-      <c r="AY52" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ52" t="s">
+      <c r="AS52" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV52" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2489,22 +2459,19 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="AF53" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>9</v>
+      <c r="AE53" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>14</v>
       </c>
       <c r="AM53" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO53" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ53" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV53" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2518,22 +2485,19 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="AF54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" t="s">
-        <v>9</v>
+      <c r="AE54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>14</v>
       </c>
       <c r="AN54" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO54" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP54" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ54" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV54" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2547,22 +2511,19 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="AG55" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ55" t="s">
-        <v>9</v>
+      <c r="AF55" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM55" t="s">
+        <v>14</v>
       </c>
       <c r="AN55" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP55" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ55" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2576,11 +2537,14 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="AG56" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ56" t="s">
-        <v>9</v>
+      <c r="AF56" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM56" t="s">
+        <v>16</v>
       </c>
       <c r="AN56" t="s">
         <v>16</v>
@@ -2589,22 +2553,22 @@
         <v>16</v>
       </c>
       <c r="AP56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR56" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="AS56" t="s">
         <v>15</v>
       </c>
       <c r="AT56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV56" t="s">
         <v>14</v>
@@ -2613,15 +2577,6 @@
         <v>14</v>
       </c>
       <c r="AX56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ56" t="s">
-        <v>21</v>
-      </c>
-      <c r="BA56" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2635,25 +2590,25 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="AI57" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR57" t="s">
+      <c r="AH57" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP57" t="s">
         <v>33</v>
       </c>
+      <c r="AX57" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>14</v>
+      </c>
       <c r="AZ57" t="s">
         <v>14</v>
       </c>
       <c r="BA57" t="s">
-        <v>14</v>
-      </c>
-      <c r="BB57" t="s">
-        <v>14</v>
-      </c>
-      <c r="BC57" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2667,19 +2622,19 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="AI58" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK58" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR58" t="s">
+      <c r="AH58" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP58" t="s">
         <v>33</v>
       </c>
-      <c r="BC58" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD58" t="s">
+      <c r="BA58" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB58" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2693,22 +2648,31 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
+      <c r="AI59" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ59" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ59" t="s">
+        <v>34</v>
       </c>
       <c r="AR59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AS59" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AT59" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD59" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU59" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB59" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2722,22 +2686,22 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
+      <c r="AI60" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT60" t="s">
         <v>33</v>
       </c>
-      <c r="AT60" t="s">
-        <v>14</v>
-      </c>
       <c r="AU60" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD60" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB60" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2751,19 +2715,19 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
+      <c r="AJ61" t="s">
+        <v>5</v>
+      </c>
       <c r="AK61" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS61" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AT61" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD61" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB61" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2777,32 +2741,29 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="AK62" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS62" t="s">
-        <v>16</v>
+      <c r="AJ62" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" t="s">
+        <v>9</v>
       </c>
       <c r="AT62" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="AU62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV62" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="AW62" t="s">
         <v>15</v>
       </c>
       <c r="AX62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ62" t="s">
         <v>14</v>
@@ -2811,15 +2772,9 @@
         <v>14</v>
       </c>
       <c r="BB62" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BC62" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD62" t="s">
-        <v>21</v>
-      </c>
-      <c r="BE62" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2833,15 +2788,21 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="AK63" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR63" t="s">
-        <v>9</v>
-      </c>
-      <c r="AV63" t="s">
+      <c r="AJ63" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU63" t="s">
         <v>33</v>
       </c>
+      <c r="BB63" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC63" t="s">
+        <v>14</v>
+      </c>
       <c r="BD63" t="s">
         <v>14</v>
       </c>
@@ -2849,9 +2810,6 @@
         <v>14</v>
       </c>
       <c r="BF63" t="s">
-        <v>14</v>
-      </c>
-      <c r="BG63" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2865,31 +2823,19 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="AK64" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AV64" t="s">
-        <v>16</v>
-      </c>
-      <c r="AW64" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX64" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY64" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ64" t="s">
+      <c r="AJ64" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU64" t="s">
         <v>33</v>
       </c>
+      <c r="BF64" t="s">
+        <v>14</v>
+      </c>
       <c r="BG64" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH64" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2903,22 +2849,19 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="AL65" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR65" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ65" t="s">
-        <v>33</v>
-      </c>
-      <c r="BA65" t="s">
-        <v>14</v>
-      </c>
-      <c r="BB65" t="s">
-        <v>21</v>
-      </c>
-      <c r="BH65" t="s">
+      <c r="AK65" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU65" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG65" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2932,22 +2875,22 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
-      <c r="AN66" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR66" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ66" t="s">
+      <c r="AM66" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU66" t="s">
         <v>33</v>
       </c>
-      <c r="BB66" t="s">
-        <v>14</v>
-      </c>
-      <c r="BC66" t="s">
-        <v>21</v>
-      </c>
-      <c r="BH66" t="s">
+      <c r="AV66" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW66" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG66" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2961,22 +2904,25 @@
       <c r="C67" t="s">
         <v>35</v>
       </c>
-      <c r="BC67" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD67" t="s">
-        <v>9</v>
-      </c>
-      <c r="BE67" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF67" t="s">
-        <v>14</v>
+      <c r="AW67" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA67" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB67" t="s">
+        <v>21</v>
       </c>
       <c r="BG67" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH67" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2990,25 +2936,34 @@
       <c r="C68" t="s">
         <v>36</v>
       </c>
+      <c r="AW68" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY68" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ68" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA68" t="s">
+        <v>33</v>
+      </c>
+      <c r="BB68" t="s">
+        <v>14</v>
+      </c>
       <c r="BC68" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BD68" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BE68" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="BH68" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI68" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ68" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK68" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3022,19 +2977,19 @@
       <c r="C69" t="s">
         <v>37</v>
       </c>
-      <c r="BC69" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD69" t="s">
-        <v>9</v>
-      </c>
-      <c r="BE69" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF69" t="s">
-        <v>21</v>
-      </c>
-      <c r="BK69" t="s">
+      <c r="AW69" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA69" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB69" t="s">
+        <v>21</v>
+      </c>
+      <c r="BH69" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3048,19 +3003,19 @@
       <c r="C70" t="s">
         <v>38</v>
       </c>
-      <c r="BC70" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD70" t="s">
-        <v>9</v>
-      </c>
-      <c r="BE70" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF70" t="s">
-        <v>21</v>
-      </c>
-      <c r="BK70" t="s">
+      <c r="AW70" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA70" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB70" t="s">
+        <v>21</v>
+      </c>
+      <c r="BH70" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3074,28 +3029,34 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
+      <c r="AX71" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA71" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB71" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC71" t="s">
+        <v>15</v>
+      </c>
       <c r="BD71" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BE71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BF71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BG71" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH71" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI71" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ71" t="s">
-        <v>21</v>
-      </c>
-      <c r="BK71" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3109,28 +3070,34 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
+      <c r="AX72" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB72" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC72" t="s">
+        <v>16</v>
+      </c>
       <c r="BD72" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BE72" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="BG72" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BH72" t="s">
-        <v>33</v>
+        <v>14</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>14</v>
       </c>
       <c r="BJ72" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK72" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL72" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM72" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3144,14 +3111,23 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
-      <c r="BD73" t="s">
-        <v>5</v>
+      <c r="AX73" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>9</v>
       </c>
       <c r="BE73" t="s">
-        <v>9</v>
-      </c>
-      <c r="BH73" t="s">
         <v>33</v>
+      </c>
+      <c r="BJ73" t="s">
+        <v>15</v>
+      </c>
+      <c r="BK73" t="s">
+        <v>15</v>
+      </c>
+      <c r="BL73" t="s">
+        <v>15</v>
       </c>
       <c r="BM73" t="s">
         <v>14</v>
@@ -3179,25 +3155,25 @@
       <c r="C74" t="s">
         <v>23</v>
       </c>
-      <c r="BD74" t="s">
-        <v>5</v>
+      <c r="AX74" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY74" t="s">
+        <v>9</v>
       </c>
       <c r="BE74" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG74" t="s">
+        <v>14</v>
       </c>
       <c r="BH74" t="s">
         <v>14</v>
       </c>
       <c r="BI74" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ74" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK74" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL74" t="s">
         <v>21</v>
       </c>
       <c r="BQ74" t="s">
@@ -3214,11 +3190,20 @@
       <c r="C75" t="s">
         <v>24</v>
       </c>
+      <c r="AY75" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ75" t="s">
+        <v>9</v>
+      </c>
       <c r="BE75" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BF75" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="BG75" t="s">
+        <v>14</v>
       </c>
       <c r="BH75" t="s">
         <v>14</v>
@@ -3230,15 +3215,6 @@
         <v>14</v>
       </c>
       <c r="BK75" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL75" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM75" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN75" t="s">
         <v>21</v>
       </c>
       <c r="BQ75" t="s">
@@ -3255,16 +3231,16 @@
       <c r="C76" t="s">
         <v>25</v>
       </c>
-      <c r="BE76" t="s">
-        <v>5</v>
+      <c r="AY76" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ76" t="s">
+        <v>9</v>
       </c>
       <c r="BF76" t="s">
-        <v>9</v>
-      </c>
-      <c r="BI76" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ76" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG76" t="s">
         <v>21</v>
       </c>
       <c r="BQ76" t="s">
@@ -3281,19 +3257,19 @@
       <c r="C77" t="s">
         <v>13</v>
       </c>
-      <c r="BE77" t="s">
-        <v>5</v>
+      <c r="AY77" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ77" t="s">
+        <v>9</v>
       </c>
       <c r="BF77" t="s">
-        <v>9</v>
-      </c>
-      <c r="BI77" t="s">
-        <v>15</v>
-      </c>
-      <c r="BJ77" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK77" t="s">
+        <v>15</v>
+      </c>
+      <c r="BG77" t="s">
+        <v>14</v>
+      </c>
+      <c r="BH77" t="s">
         <v>21</v>
       </c>
       <c r="BR77" t="s">
@@ -3310,19 +3286,19 @@
       <c r="C78" t="s">
         <v>26</v>
       </c>
-      <c r="BE78" t="s">
-        <v>5</v>
+      <c r="AY78" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA78" t="s">
+        <v>9</v>
       </c>
       <c r="BF78" t="s">
-        <v>9</v>
-      </c>
-      <c r="BI78" t="s">
-        <v>33</v>
-      </c>
-      <c r="BJ78" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK78" t="s">
+        <v>15</v>
+      </c>
+      <c r="BG78" t="s">
+        <v>14</v>
+      </c>
+      <c r="BH78" t="s">
         <v>21</v>
       </c>
       <c r="BR78" t="s">
@@ -3339,22 +3315,22 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
+      <c r="AZ79" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB79" t="s">
+        <v>9</v>
+      </c>
       <c r="BF79" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="BG79" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="BH79" t="s">
+        <v>14</v>
       </c>
       <c r="BI79" t="s">
-        <v>33</v>
-      </c>
-      <c r="BJ79" t="s">
-        <v>15</v>
-      </c>
-      <c r="BK79" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL79" t="s">
         <v>21</v>
       </c>
       <c r="BR79" t="s">
@@ -3371,46 +3347,34 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="BF80" t="s">
-        <v>5</v>
+      <c r="AZ80" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB80" t="s">
+        <v>9</v>
       </c>
       <c r="BG80" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="BH80" t="s">
+        <v>16</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>14</v>
       </c>
       <c r="BJ80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BK80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BL80" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BM80" t="s">
-        <v>15</v>
-      </c>
-      <c r="BN80" t="s">
-        <v>15</v>
-      </c>
-      <c r="BO80" t="s">
-        <v>15</v>
-      </c>
-      <c r="BP80" t="s">
-        <v>15</v>
-      </c>
-      <c r="BQ80" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BR80" t="s">
-        <v>14</v>
-      </c>
-      <c r="BS80" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT80" t="s">
-        <v>14</v>
-      </c>
-      <c r="BU80" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3424,25 +3388,28 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="BF81" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG81" t="s">
-        <v>9</v>
-      </c>
-      <c r="BL81" t="s">
+      <c r="AZ81" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC81" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI81" t="s">
         <v>33</v>
       </c>
-      <c r="BU81" t="s">
-        <v>14</v>
-      </c>
-      <c r="BV81" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW81" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX81" t="s">
+      <c r="BM81" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN81" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO81" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP81" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS81" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3456,19 +3423,22 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="BF82" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG82" t="s">
-        <v>9</v>
-      </c>
-      <c r="BL82" t="s">
+      <c r="BA82" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI82" t="s">
         <v>33</v>
       </c>
-      <c r="BX82" t="s">
-        <v>14</v>
-      </c>
-      <c r="BY82" t="s">
+      <c r="BP82" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ82" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS82" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3482,22 +3452,19 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
-      <c r="BG83" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH83" t="s">
-        <v>9</v>
-      </c>
-      <c r="BL83" t="s">
-        <v>33</v>
-      </c>
-      <c r="BM83" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN83" t="s">
-        <v>21</v>
-      </c>
-      <c r="BY83" t="s">
+      <c r="BB83" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF83" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS83" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3511,22 +3478,19 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
-      <c r="BG84" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH84" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM84" t="s">
-        <v>33</v>
-      </c>
-      <c r="BN84" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO84" t="s">
-        <v>21</v>
-      </c>
-      <c r="BY84" t="s">
+      <c r="BB84" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF84" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK84" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS84" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3540,22 +3504,19 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
-      <c r="BH85" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI85" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM85" t="s">
-        <v>33</v>
-      </c>
-      <c r="BN85" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO85" t="s">
-        <v>21</v>
-      </c>
-      <c r="BY85" t="s">
+      <c r="BC85" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG85" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ85" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK85" t="s">
+        <v>21</v>
+      </c>
+      <c r="BT85" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3569,52 +3530,46 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="BH86" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI86" t="s">
-        <v>9</v>
+      <c r="BC86" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG86" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ86" t="s">
+        <v>16</v>
+      </c>
+      <c r="BK86" t="s">
+        <v>16</v>
+      </c>
+      <c r="BL86" t="s">
+        <v>16</v>
       </c>
       <c r="BM86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BO86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BP86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ86" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BR86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BS86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BT86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BU86" t="s">
-        <v>14</v>
-      </c>
-      <c r="BV86" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW86" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX86" t="s">
-        <v>14</v>
-      </c>
-      <c r="BY86" t="s">
-        <v>21</v>
-      </c>
-      <c r="BZ86" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3628,25 +3583,25 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
+      <c r="BF87" t="s">
+        <v>5</v>
+      </c>
       <c r="BH87" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK87" t="s">
-        <v>9</v>
-      </c>
-      <c r="BQ87" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM87" t="s">
         <v>33</v>
       </c>
-      <c r="BY87" t="s">
-        <v>14</v>
-      </c>
-      <c r="BZ87" t="s">
-        <v>14</v>
-      </c>
-      <c r="CA87" t="s">
-        <v>14</v>
-      </c>
-      <c r="CB87" t="s">
+      <c r="BU87" t="s">
+        <v>14</v>
+      </c>
+      <c r="BV87" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW87" t="s">
+        <v>14</v>
+      </c>
+      <c r="BX87" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3660,19 +3615,19 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
+      <c r="BF88" t="s">
+        <v>5</v>
+      </c>
       <c r="BH88" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK88" t="s">
-        <v>9</v>
-      </c>
-      <c r="BQ88" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM88" t="s">
         <v>33</v>
       </c>
-      <c r="CB88" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC88" t="s">
+      <c r="BX88" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY88" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3686,22 +3641,31 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
-      <c r="BI89" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK89" t="s">
-        <v>9</v>
+      <c r="BG89" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH89" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM89" t="s">
+        <v>34</v>
+      </c>
+      <c r="BN89" t="s">
+        <v>34</v>
+      </c>
+      <c r="BO89" t="s">
+        <v>34</v>
+      </c>
+      <c r="BP89" t="s">
+        <v>34</v>
       </c>
       <c r="BQ89" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BR89" t="s">
-        <v>14</v>
-      </c>
-      <c r="BS89" t="s">
-        <v>21</v>
-      </c>
-      <c r="CC89" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY89" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3715,22 +3679,22 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
-      <c r="BI90" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK90" t="s">
-        <v>9</v>
+      <c r="BG90" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH90" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ90" t="s">
+        <v>33</v>
       </c>
       <c r="BR90" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BS90" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT90" t="s">
-        <v>21</v>
-      </c>
-      <c r="CC90" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY90" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3744,19 +3708,19 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
-      <c r="BK91" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL91" t="s">
-        <v>9</v>
+      <c r="BH91" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI91" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ91" t="s">
+        <v>14</v>
       </c>
       <c r="BR91" t="s">
-        <v>14</v>
-      </c>
-      <c r="BS91" t="s">
-        <v>21</v>
-      </c>
-      <c r="CC91" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY91" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3770,49 +3734,40 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="BK92" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM92" t="s">
-        <v>9</v>
+      <c r="BH92" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ92" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ92" t="s">
+        <v>33</v>
       </c>
       <c r="BR92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BS92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BT92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU92" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BV92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BW92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BX92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BY92" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BZ92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CA92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CB92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC92" t="s">
-        <v>21</v>
-      </c>
-      <c r="CD92" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3826,25 +3781,28 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="BK93" t="s">
+      <c r="BH93" t="s">
         <v>5</v>
       </c>
       <c r="BQ93" t="s">
         <v>9</v>
       </c>
-      <c r="BU93" t="s">
+      <c r="BR93" t="s">
         <v>33</v>
       </c>
+      <c r="BY93" t="s">
+        <v>15</v>
+      </c>
+      <c r="BZ93" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA93" t="s">
+        <v>14</v>
+      </c>
+      <c r="CB93" t="s">
+        <v>14</v>
+      </c>
       <c r="CC93" t="s">
-        <v>14</v>
-      </c>
-      <c r="CD93" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE93" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF93" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3858,31 +3816,19 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="BK94" t="s">
+      <c r="BH94" t="s">
         <v>5</v>
       </c>
       <c r="BQ94" t="s">
         <v>9</v>
       </c>
-      <c r="BU94" t="s">
-        <v>16</v>
-      </c>
-      <c r="BV94" t="s">
-        <v>16</v>
-      </c>
-      <c r="BW94" t="s">
-        <v>16</v>
-      </c>
-      <c r="BX94" t="s">
-        <v>16</v>
-      </c>
-      <c r="BY94" t="s">
+      <c r="BR94" t="s">
         <v>33</v>
       </c>
-      <c r="CF94" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG94" t="s">
+      <c r="CC94" t="s">
+        <v>14</v>
+      </c>
+      <c r="CD94" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3896,22 +3842,19 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
-      <c r="BL95" t="s">
+      <c r="BI95" t="s">
         <v>5</v>
       </c>
       <c r="BQ95" t="s">
         <v>9</v>
       </c>
-      <c r="BY95" t="s">
-        <v>33</v>
-      </c>
-      <c r="BZ95" t="s">
-        <v>14</v>
-      </c>
-      <c r="CA95" t="s">
-        <v>21</v>
-      </c>
-      <c r="CG95" t="s">
+      <c r="BR95" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS95" t="s">
+        <v>21</v>
+      </c>
+      <c r="CD95" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3925,22 +3868,22 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
-      <c r="BM96" t="s">
+      <c r="BJ96" t="s">
         <v>5</v>
       </c>
       <c r="BQ96" t="s">
         <v>9</v>
       </c>
-      <c r="BY96" t="s">
+      <c r="BR96" t="s">
         <v>33</v>
       </c>
-      <c r="CA96" t="s">
-        <v>14</v>
-      </c>
-      <c r="CB96" t="s">
-        <v>21</v>
-      </c>
-      <c r="CG96" t="s">
+      <c r="BS96" t="s">
+        <v>14</v>
+      </c>
+      <c r="BT96" t="s">
+        <v>21</v>
+      </c>
+      <c r="CD96" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3954,22 +3897,25 @@
       <c r="C97" t="s">
         <v>35</v>
       </c>
-      <c r="CB97" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC97" t="s">
-        <v>9</v>
+      <c r="BT97" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU97" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV97" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW97" t="s">
+        <v>14</v>
+      </c>
+      <c r="BX97" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY97" t="s">
+        <v>21</v>
       </c>
       <c r="CD97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG97" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3983,25 +3929,34 @@
       <c r="C98" t="s">
         <v>36</v>
       </c>
+      <c r="BT98" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU98" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV98" t="s">
+        <v>16</v>
+      </c>
+      <c r="BW98" t="s">
+        <v>16</v>
+      </c>
+      <c r="BX98" t="s">
+        <v>33</v>
+      </c>
+      <c r="BY98" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ98" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA98" t="s">
+        <v>14</v>
+      </c>
       <c r="CB98" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC98" t="s">
-        <v>9</v>
-      </c>
-      <c r="CD98" t="s">
-        <v>33</v>
-      </c>
-      <c r="CG98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CH98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ98" t="s">
+        <v>21</v>
+      </c>
+      <c r="CE98" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4015,19 +3970,19 @@
       <c r="C99" t="s">
         <v>37</v>
       </c>
-      <c r="CB99" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC99" t="s">
-        <v>9</v>
-      </c>
-      <c r="CD99" t="s">
-        <v>14</v>
+      <c r="BT99" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU99" t="s">
+        <v>9</v>
+      </c>
+      <c r="BX99" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY99" t="s">
+        <v>21</v>
       </c>
       <c r="CE99" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ99" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4041,16 +3996,16 @@
       <c r="C100" t="s">
         <v>38</v>
       </c>
-      <c r="CB100" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD100" t="s">
-        <v>14</v>
+      <c r="BT100" t="s">
+        <v>5</v>
+      </c>
+      <c r="BX100" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY100" t="s">
+        <v>21</v>
       </c>
       <c r="CE100" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ100" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4064,19 +4019,22 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="CC101" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD101" t="s">
-        <v>9</v>
+      <c r="BU101" t="s">
+        <v>5</v>
+      </c>
+      <c r="BV101" t="s">
+        <v>9</v>
+      </c>
+      <c r="BX101" t="s">
+        <v>16</v>
+      </c>
+      <c r="BY101" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ101" t="s">
+        <v>21</v>
       </c>
       <c r="CE101" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF101" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ101" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4090,25 +4048,22 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="CC102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD102" t="s">
-        <v>9</v>
-      </c>
-      <c r="CE102" t="s">
+      <c r="BU102" t="s">
+        <v>5</v>
+      </c>
+      <c r="BV102" t="s">
+        <v>9</v>
+      </c>
+      <c r="BY102" t="s">
         <v>16</v>
       </c>
+      <c r="BZ102" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA102" t="s">
+        <v>21</v>
+      </c>
       <c r="CF102" t="s">
-        <v>15</v>
-      </c>
-      <c r="CG102" t="s">
-        <v>14</v>
-      </c>
-      <c r="CH102" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK102" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4122,25 +4077,22 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="CC103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD103" t="s">
-        <v>9</v>
+      <c r="BU103" t="s">
+        <v>5</v>
+      </c>
+      <c r="BV103" t="s">
+        <v>9</v>
+      </c>
+      <c r="BZ103" t="s">
+        <v>16</v>
+      </c>
+      <c r="CA103" t="s">
+        <v>14</v>
+      </c>
+      <c r="CB103" t="s">
+        <v>21</v>
       </c>
       <c r="CF103" t="s">
-        <v>16</v>
-      </c>
-      <c r="CG103" t="s">
-        <v>15</v>
-      </c>
-      <c r="CH103" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI103" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK103" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4154,25 +4106,22 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
+      <c r="BU104" t="s">
+        <v>5</v>
+      </c>
+      <c r="BV104" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA104" t="s">
+        <v>16</v>
+      </c>
+      <c r="CB104" t="s">
+        <v>14</v>
+      </c>
       <c r="CC104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD104" t="s">
-        <v>9</v>
-      </c>
-      <c r="CG104" t="s">
-        <v>16</v>
-      </c>
-      <c r="CH104" t="s">
-        <v>15</v>
-      </c>
-      <c r="CI104" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ104" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK104" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF104" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4186,22 +4135,25 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
+      <c r="BV105" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW105" t="s">
+        <v>9</v>
+      </c>
+      <c r="CB105" t="s">
+        <v>16</v>
+      </c>
+      <c r="CC105" t="s">
+        <v>15</v>
+      </c>
       <c r="CD105" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CE105" t="s">
-        <v>9</v>
-      </c>
-      <c r="CH105" t="s">
-        <v>16</v>
-      </c>
-      <c r="CI105" t="s">
-        <v>15</v>
-      </c>
-      <c r="CJ105" t="s">
-        <v>14</v>
-      </c>
-      <c r="CK105" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF105" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4215,22 +4167,25 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
+      <c r="BV106" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW106" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC106" t="s">
+        <v>16</v>
+      </c>
       <c r="CD106" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CE106" t="s">
-        <v>9</v>
-      </c>
-      <c r="CI106" t="s">
-        <v>16</v>
-      </c>
-      <c r="CJ106" t="s">
-        <v>15</v>
-      </c>
-      <c r="CK106" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL106" t="s">
+        <v>14</v>
+      </c>
+      <c r="CF106" t="s">
+        <v>21</v>
+      </c>
+      <c r="CG106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4244,22 +4199,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
+      <c r="BV107" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW107" t="s">
+        <v>9</v>
+      </c>
       <c r="CD107" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="CE107" t="s">
-        <v>9</v>
-      </c>
-      <c r="CJ107" t="s">
-        <v>16</v>
-      </c>
-      <c r="CK107" t="s">
-        <v>15</v>
-      </c>
-      <c r="CL107" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM107" t="s">
+        <v>15</v>
+      </c>
+      <c r="CF107" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG107" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4273,22 +4228,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="CD108" t="s">
-        <v>5</v>
+      <c r="BV108" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW108" t="s">
+        <v>9</v>
       </c>
       <c r="CE108" t="s">
-        <v>9</v>
-      </c>
-      <c r="CK108" t="s">
         <v>16</v>
       </c>
-      <c r="CL108" t="s">
-        <v>15</v>
-      </c>
-      <c r="CM108" t="s">
-        <v>14</v>
-      </c>
-      <c r="CN108" t="s">
+      <c r="CF108" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG108" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH108" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4302,22 +4257,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="CE109" t="s">
-        <v>5</v>
+      <c r="BW109" t="s">
+        <v>5</v>
+      </c>
+      <c r="BX109" t="s">
+        <v>9</v>
       </c>
       <c r="CF109" t="s">
-        <v>9</v>
-      </c>
-      <c r="CL109" t="s">
         <v>16</v>
       </c>
-      <c r="CM109" t="s">
-        <v>15</v>
-      </c>
-      <c r="CN109" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO109" t="s">
+      <c r="CG109" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH109" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI109" t="s">
         <v>22</v>
       </c>
     </row>

--- a/project/outputs_xlsx_solution/test33.4-wide.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide.xlsx
@@ -831,6 +831,12 @@
       <c r="CI1">
         <v>84</v>
       </c>
+      <c r="CJ1">
+        <v>85</v>
+      </c>
+      <c r="CK1">
+        <v>86</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -2025,6 +2031,9 @@
       <c r="Z40" t="s">
         <v>5</v>
       </c>
+      <c r="AA40" t="s">
+        <v>9</v>
+      </c>
       <c r="AD40" t="s">
         <v>14</v>
       </c>
@@ -2045,20 +2054,11 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AA41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>16</v>
-      </c>
       <c r="AE41" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AF41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG41" t="s">
         <v>14</v>
@@ -2083,17 +2083,11 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AA42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" t="s">
-        <v>9</v>
-      </c>
       <c r="AE42" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AF42" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AG42" t="s">
         <v>16</v>
@@ -2124,10 +2118,10 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AA43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" t="s">
+      <c r="AE43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" t="s">
         <v>9</v>
       </c>
       <c r="AH43" t="s">
@@ -2168,10 +2162,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AA44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" t="s">
+      <c r="AE44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" t="s">
         <v>9</v>
       </c>
       <c r="AH44" t="s">
@@ -2203,10 +2197,10 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AB45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" t="s">
+      <c r="AF45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" t="s">
         <v>9</v>
       </c>
       <c r="AH45" t="s">
@@ -2244,10 +2238,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AB46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" t="s">
+      <c r="AF46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" t="s">
         <v>9</v>
       </c>
       <c r="AI46" t="s">
@@ -2270,10 +2264,10 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AB47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" t="s">
+      <c r="AF47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" t="s">
         <v>9</v>
       </c>
       <c r="AI47" t="s">
@@ -2299,10 +2293,10 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AB48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" t="s">
+      <c r="AF48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" t="s">
         <v>9</v>
       </c>
       <c r="AI48" t="s">
@@ -2325,10 +2319,10 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AC49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" t="s">
+      <c r="AG49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" t="s">
         <v>9</v>
       </c>
       <c r="AI49" t="s">
@@ -2354,10 +2348,10 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AC50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE50" t="s">
+      <c r="AG50" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH50" t="s">
         <v>9</v>
       </c>
       <c r="AJ50" t="s">
@@ -2395,10 +2389,10 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AC51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF51" t="s">
+      <c r="AG51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH51" t="s">
         <v>9</v>
       </c>
       <c r="AL51" t="s">
@@ -2430,10 +2424,10 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AD52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" t="s">
+      <c r="AG52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" t="s">
         <v>9</v>
       </c>
       <c r="AL52" t="s">
@@ -2459,10 +2453,10 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="AE53" t="s">
-        <v>5</v>
-      </c>
       <c r="AH53" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI53" t="s">
         <v>9</v>
       </c>
       <c r="AL53" t="s">
@@ -2485,10 +2479,10 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="AE54" t="s">
-        <v>5</v>
-      </c>
       <c r="AH54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" t="s">
         <v>9</v>
       </c>
       <c r="AM54" t="s">
@@ -2511,10 +2505,10 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="AF55" t="s">
-        <v>5</v>
-      </c>
       <c r="AI55" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ55" t="s">
         <v>9</v>
       </c>
       <c r="AM55" t="s">
@@ -2537,10 +2531,10 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="AF56" t="s">
-        <v>5</v>
-      </c>
       <c r="AI56" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ56" t="s">
         <v>9</v>
       </c>
       <c r="AM56" t="s">
@@ -2590,7 +2584,7 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="AH57" t="s">
+      <c r="AI57" t="s">
         <v>5</v>
       </c>
       <c r="AJ57" t="s">
@@ -2622,7 +2616,7 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="AH58" t="s">
+      <c r="AI58" t="s">
         <v>5</v>
       </c>
       <c r="AJ58" t="s">
@@ -2648,10 +2642,10 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="AI59" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" t="s">
         <v>9</v>
       </c>
       <c r="AP59" t="s">
@@ -2686,10 +2680,10 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="AI60" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" t="s">
         <v>9</v>
       </c>
       <c r="AT60" t="s">
@@ -2715,10 +2709,10 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="AJ61" t="s">
-        <v>5</v>
-      </c>
       <c r="AK61" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL61" t="s">
         <v>9</v>
       </c>
       <c r="AT61" t="s">
@@ -2741,7 +2735,7 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="AJ62" t="s">
+      <c r="AK62" t="s">
         <v>5</v>
       </c>
       <c r="AM62" t="s">
@@ -2788,7 +2782,7 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="AJ63" t="s">
+      <c r="AK63" t="s">
         <v>5</v>
       </c>
       <c r="AT63" t="s">
@@ -2823,7 +2817,7 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="AJ64" t="s">
+      <c r="AK64" t="s">
         <v>5</v>
       </c>
       <c r="AT64" t="s">
@@ -2849,7 +2843,7 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="AK65" t="s">
+      <c r="AL65" t="s">
         <v>5</v>
       </c>
       <c r="AT65" t="s">
@@ -3999,6 +3993,9 @@
       <c r="BT100" t="s">
         <v>5</v>
       </c>
+      <c r="BU100" t="s">
+        <v>9</v>
+      </c>
       <c r="BX100" t="s">
         <v>14</v>
       </c>
@@ -4019,19 +4016,16 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="BU101" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV101" t="s">
-        <v>9</v>
-      </c>
-      <c r="BX101" t="s">
-        <v>16</v>
-      </c>
       <c r="BY101" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BZ101" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA101" t="s">
+        <v>14</v>
+      </c>
+      <c r="CB101" t="s">
         <v>21</v>
       </c>
       <c r="CE101" t="s">
@@ -4048,19 +4042,19 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="BU102" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV102" t="s">
-        <v>9</v>
-      </c>
       <c r="BY102" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ102" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA102" t="s">
         <v>16</v>
       </c>
-      <c r="BZ102" t="s">
-        <v>14</v>
-      </c>
-      <c r="CA102" t="s">
+      <c r="CB102" t="s">
+        <v>14</v>
+      </c>
+      <c r="CC102" t="s">
         <v>21</v>
       </c>
       <c r="CF102" t="s">
@@ -4077,19 +4071,22 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="BU103" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV103" t="s">
-        <v>9</v>
+      <c r="BY103" t="s">
+        <v>5</v>
       </c>
       <c r="BZ103" t="s">
+        <v>9</v>
+      </c>
+      <c r="CB103" t="s">
         <v>16</v>
       </c>
-      <c r="CA103" t="s">
-        <v>14</v>
-      </c>
-      <c r="CB103" t="s">
+      <c r="CC103" t="s">
+        <v>15</v>
+      </c>
+      <c r="CD103" t="s">
+        <v>14</v>
+      </c>
+      <c r="CE103" t="s">
         <v>21</v>
       </c>
       <c r="CF103" t="s">
@@ -4106,20 +4103,20 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="BU104" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV104" t="s">
-        <v>9</v>
-      </c>
-      <c r="CA104" t="s">
+      <c r="BY104" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ104" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC104" t="s">
         <v>16</v>
       </c>
-      <c r="CB104" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC104" t="s">
-        <v>21</v>
+      <c r="CD104" t="s">
+        <v>15</v>
+      </c>
+      <c r="CE104" t="s">
+        <v>14</v>
       </c>
       <c r="CF104" t="s">
         <v>22</v>
@@ -4135,25 +4132,22 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="BV105" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW105" t="s">
-        <v>9</v>
-      </c>
-      <c r="CB105" t="s">
+      <c r="BZ105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA105" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD105" t="s">
         <v>16</v>
       </c>
-      <c r="CC105" t="s">
-        <v>15</v>
-      </c>
-      <c r="CD105" t="s">
-        <v>14</v>
-      </c>
       <c r="CE105" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CF105" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG105" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4167,25 +4161,22 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="BV106" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW106" t="s">
-        <v>9</v>
-      </c>
-      <c r="CC106" t="s">
+      <c r="BZ106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA106" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE106" t="s">
         <v>16</v>
       </c>
-      <c r="CD106" t="s">
-        <v>15</v>
-      </c>
-      <c r="CE106" t="s">
-        <v>14</v>
-      </c>
       <c r="CF106" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CG106" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4199,22 +4190,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="BV107" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW107" t="s">
-        <v>9</v>
-      </c>
-      <c r="CD107" t="s">
+      <c r="BZ107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA107" t="s">
+        <v>9</v>
+      </c>
+      <c r="CF107" t="s">
         <v>16</v>
       </c>
-      <c r="CE107" t="s">
-        <v>15</v>
-      </c>
-      <c r="CF107" t="s">
-        <v>14</v>
-      </c>
       <c r="CG107" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH107" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI107" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4228,22 +4219,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="BV108" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW108" t="s">
-        <v>9</v>
-      </c>
-      <c r="CE108" t="s">
+      <c r="BZ108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA108" t="s">
+        <v>9</v>
+      </c>
+      <c r="CG108" t="s">
         <v>16</v>
       </c>
-      <c r="CF108" t="s">
-        <v>15</v>
-      </c>
-      <c r="CG108" t="s">
-        <v>14</v>
-      </c>
       <c r="CH108" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI108" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ108" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4257,22 +4248,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="BW109" t="s">
-        <v>5</v>
-      </c>
-      <c r="BX109" t="s">
-        <v>9</v>
-      </c>
-      <c r="CF109" t="s">
+      <c r="CA109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB109" t="s">
+        <v>9</v>
+      </c>
+      <c r="CH109" t="s">
         <v>16</v>
       </c>
-      <c r="CG109" t="s">
-        <v>15</v>
-      </c>
-      <c r="CH109" t="s">
-        <v>14</v>
-      </c>
       <c r="CI109" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ109" t="s">
+        <v>14</v>
+      </c>
+      <c r="CK109" t="s">
         <v>22</v>
       </c>
     </row>
